--- a/ОИИ/3 (Степени принадлежности).xlsx
+++ b/ОИИ/3 (Степени принадлежности).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>Категория</t>
   </si>
@@ -22,13 +22,13 @@
     <t>Значение</t>
   </si>
   <si>
-    <t>Персональный компьютер типа IBM PC</t>
+    <t>ПК (IBM PC)</t>
   </si>
   <si>
     <t>Ноутбук</t>
   </si>
   <si>
-    <t>Карманный персональный компьютер (КПК)</t>
+    <t>КПК</t>
   </si>
 </sst>
 </file>
@@ -96,13 +96,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Персональный компьютер типа IBM PC</c:v>
+                  <c:v>ПК (IBM PC)</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Ноутбук</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Карманный персональный компьютер (КПК)</c:v>
+                  <c:v>КПК</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -114,13 +114,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.1094522895155198</c:v>
+                  <c:v>0.649</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3089956436328642</c:v>
+                  <c:v>0.229</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.581552066851616</c:v>
+                  <c:v>0.122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -170,19 +170,114 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Значения</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$A$17:$A$19</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ПК (IBM PC)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Ноутбук</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>КПК</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$B$17:$B$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.753</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.182</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.064</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50020001"/>
+        <c:axId val="50020002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50020001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50020002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50020002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50020001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -197,6 +292,36 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -490,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -506,7 +631,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.1094522895155198</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -514,7 +639,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.3089956436328642</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -522,7 +647,39 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.581552066851616</v>
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>0.753</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>0.182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19">
+        <v>0.064</v>
       </c>
     </row>
   </sheetData>

--- a/ОИИ/3 (Степени принадлежности).xlsx
+++ b/ОИИ/3 (Степени принадлежности).xlsx
@@ -187,7 +187,7 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Лист1!$A$17:$A$19</c:f>
+              <c:f>Лист1!$A$19:$A$21</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -204,7 +204,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Лист1!$B$17:$B$19</c:f>
+              <c:f>Лист1!$B$19:$B$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -301,13 +301,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -615,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -650,35 +650,35 @@
         <v>0.122</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>2</v>
-      </c>
-      <c r="B17">
-        <v>0.753</v>
-      </c>
-    </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18">
-        <v>0.182</v>
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>0.753</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>0.182</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
         <v>4</v>
       </c>
-      <c r="B19">
+      <c r="B21">
         <v>0.064</v>
       </c>
     </row>
